--- a/docs/bess-screenshot-index.xlsx
+++ b/docs/bess-screenshot-index.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="281">
   <si>
     <t>#</t>
   </si>
@@ -45,6 +45,726 @@
   </si>
   <si>
     <t>Reference id</t>
+  </si>
+  <si>
+    <t>1 — Essential</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>bess/access/license-window.png</t>
+  </si>
+  <si>
+    <t>The License window</t>
+  </si>
+  <si>
+    <t>Help ▸ License… on a device with no active access: the ✗ No access status headline and message, the Your Device ID (identifies this computer to SolarLayout:) field with its Copy button, and the Get Free Access, Contact Us, Refresh and Close buttons.</t>
+  </si>
+  <si>
+    <t>Launch the app on a device with no active access, then open Help ▸ License…</t>
+  </si>
+  <si>
+    <t>Number the Device ID field 1, the Copy button 2, and Get Free Access 3. Blur the Device ID value.</t>
+  </si>
+  <si>
+    <t>/docs/bess/access/activate</t>
+  </si>
+  <si>
+    <t>The License window on a device with no active access, showing the Device ID field, its Copy button, and the Get Free Access button.</t>
+  </si>
+  <si>
+    <t>bess-access-license-window</t>
+  </si>
+  <si>
+    <t>bess/analysis/optimise/scenario-comparison.png</t>
+  </si>
+  <si>
+    <t>The Scenario Comparison window</t>
+  </si>
+  <si>
+    <t>The whole Scenario Comparison window: the three scenario columns with their row values, the shaded highest-IRR column and winning cells, the bottom banner, and each column's Apply button plus the Close button.</t>
+  </si>
+  <si>
+    <t>Run ⚙ Optimise to completion. The Scenario Comparison window opens on its own once the search finishes.</t>
+  </si>
+  <si>
+    <t>Circle the shaded highest-IRR column header and the bottom banner.</t>
+  </si>
+  <si>
+    <t>/docs/bess/analysis/optimise</t>
+  </si>
+  <si>
+    <t>The Optimisation — Scenario Comparison window, with one column per scenario and Apply buttons beneath each.</t>
+  </si>
+  <si>
+    <t>bess-analysis-optimise-scenario-comparison</t>
+  </si>
+  <si>
+    <t>bess/exports/file-menu.png</t>
+  </si>
+  <si>
+    <t>The File menu's report and data exports</t>
+  </si>
+  <si>
+    <t>The File menu open, showing Save Project (.slb)…, Open Project (.slb)…, Load Generation CSV…, Export PDF Report…, Export Plot (PNG)…, Save Project Report (Word)…, Export Report (TXT)…, Export DFR CSV…, and Export Time-Series CSV (Dashboard Data)…, in that order.</t>
+  </si>
+  <si>
+    <t>Click File in the menu bar and capture it open, without clicking any item.</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>/docs/bess/exports/pdf-report</t>
+  </si>
+  <si>
+    <t>The File menu open, listing the project save/open actions above every report and data export action.</t>
+  </si>
+  <si>
+    <t>bess-exports-pdf-report-file-menu</t>
+  </si>
+  <si>
+    <t>bess/first-analysis/dashboard.png</t>
+  </si>
+  <si>
+    <t>The Dashboard after a run</t>
+  </si>
+  <si>
+    <t>The whole Dashboard tab after a completed run: the header strip reporting Solar/Wind/BESS size and IRR/Contracted Capacity, all six panels, and the day slider beneath the first two.</t>
+  </si>
+  <si>
+    <t>Run Simulate to completion. The result notebook switches to the Dashboard tab on its own.</t>
+  </si>
+  <si>
+    <t>Number the six panels 1 to 6 in reading order.</t>
+  </si>
+  <si>
+    <t>/docs/bess/first-analysis</t>
+  </si>
+  <si>
+    <t>The Dashboard tab after Simulate finishes, showing the header strip and all six panels.</t>
+  </si>
+  <si>
+    <t>bess-first-analysis-dashboard</t>
+  </si>
+  <si>
+    <t>bess/getting-started/window.png</t>
+  </si>
+  <si>
+    <t>The main window before an analysis</t>
+  </si>
+  <si>
+    <t>The whole window at first launch: the top banner, the menu bar, the left input notebook on its first tab, and the empty right-hand result notebook.</t>
+  </si>
+  <si>
+    <t>Launch the app fresh, before loading a generation profile or clicking Simulate. Maximise the window.</t>
+  </si>
+  <si>
+    <t>Bracket the left third and label it Input notebook; bracket the right and label it Result notebook.</t>
+  </si>
+  <si>
+    <t>/docs/bess/getting-started</t>
+  </si>
+  <si>
+    <t>The main window straight after launch, before a generation profile is loaded or a run has been made.</t>
+  </si>
+  <si>
+    <t>bess-getting-started-window</t>
+  </si>
+  <si>
+    <t>bess/inputs/bess.png</t>
+  </si>
+  <si>
+    <t>The BESS tab</t>
+  </si>
+  <si>
+    <t>The BESS tab groups in order: the RTE Mode radio and its Fixed-mode field, Depth of Discharge and Initial SOH, the Battery EOL basis radio with its Years-basis field, C-Rate, the EOL Strategy radio, and the SOH Degradation radio with its Linear fields.</t>
+  </si>
+  <si>
+    <t>Open the BESS tab. Leave the default values — Fixed RTE, Years EOL basis, Replacement strategy, Linear SOH degradation; scroll the panel to capture each group.</t>
+  </si>
+  <si>
+    <t>/docs/bess/inputs/bess</t>
+  </si>
+  <si>
+    <t>The BESS tab's RTE mode, DoD/SOH fields, EOL basis radio, C-Rate, EOL strategy and SOH degradation groups.</t>
+  </si>
+  <si>
+    <t>bess-inputs-bess</t>
+  </si>
+  <si>
+    <t>bess/inputs/data.png</t>
+  </si>
+  <si>
+    <t>The Data tab</t>
+  </si>
+  <si>
+    <t>The Generation Data File group: the CSV Path entry, the Browse… button, the Load &amp; Preview CSV button, the status line beneath, and the CSV Format Requirements note.</t>
+  </si>
+  <si>
+    <t>Open the Data tab. Leave the default state — CSV Path empty, status line reading No file loaded.</t>
+  </si>
+  <si>
+    <t>/docs/bess/inputs/data</t>
+  </si>
+  <si>
+    <t>The Data tab's CSV Path field, Browse and Load &amp; Preview CSV buttons, and the CSV format note.</t>
+  </si>
+  <si>
+    <t>bess-inputs-data</t>
+  </si>
+  <si>
+    <t>bess/inputs/finance.png</t>
+  </si>
+  <si>
+    <t>The Finance tab</t>
+  </si>
+  <si>
+    <t>The Finance tab groups in order: Discounting &amp; Escalation, the LCOE Energy Basis combobox, Payment Delay/Working Capital, the Enable debt and Enable tax checkboxes with their sub-fields, and Advanced Tech-Economic.</t>
+  </si>
+  <si>
+    <t>Open the Finance tab. Leave Enable debt and Enable tax both unchecked, the default, so their sub-fields show disabled; scroll the panel to capture each group.</t>
+  </si>
+  <si>
+    <t>/docs/bess/inputs/finance</t>
+  </si>
+  <si>
+    <t>The Finance tab's discounting, LCOE basis, payment delay, debt and tax groups.</t>
+  </si>
+  <si>
+    <t>bess-inputs-finance</t>
+  </si>
+  <si>
+    <t>bess/inputs/opex.png</t>
+  </si>
+  <si>
+    <t>The OPEX tab</t>
+  </si>
+  <si>
+    <t>The OPEX tab groups in order: Operation &amp; Maintenance, Revenue/Export/Penalty including the Apply Annual CUF Cap checkbox, the Export Price Fixed Price/CSV radio, Grid Charging, and the Optimisation Target field.</t>
+  </si>
+  <si>
+    <t>Open the OPEX tab. Leave the default values; scroll the panel to capture each group.</t>
+  </si>
+  <si>
+    <t>/docs/bess/inputs/opex</t>
+  </si>
+  <si>
+    <t>The OPEX tab's O&amp;M, Revenue &amp; Penalty, Export Price and Grid Charging groups.</t>
+  </si>
+  <si>
+    <t>bess-inputs-opex</t>
+  </si>
+  <si>
+    <t>bess/inputs/peak-window.png</t>
+  </si>
+  <si>
+    <t>The Peak tab</t>
+  </si>
+  <si>
+    <t>The Quick Preset combobox, the 4-column by 6-row grid of 24 hour checkboxes, and the selection counter beneath it.</t>
+  </si>
+  <si>
+    <t>Open the Peak tab. Leave the default tick state — 18:00, 19:00, 20:00 and 21:00 ticked, every other hour clear.</t>
+  </si>
+  <si>
+    <t>Outline the four ticked Peak hours.</t>
+  </si>
+  <si>
+    <t>/docs/bess/inputs/peak-window</t>
+  </si>
+  <si>
+    <t>The Peak tab's Quick Preset dropdown and the 24-hour checkbox grid, with 18:00 to 21:00 ticked.</t>
+  </si>
+  <si>
+    <t>bess-inputs-peak-window</t>
+  </si>
+  <si>
+    <t>bess/inputs/sizing.png</t>
+  </si>
+  <si>
+    <t>The Sizing tab</t>
+  </si>
+  <si>
+    <t>The whole Sizing tab: the Contracted Capacity Fixed Value/CSV Profile radio, the Project/Contract Life field, all five DFR Target fields, and the Initial Sizing group (Solar Installed, Wind Installed, BESS Energy).</t>
+  </si>
+  <si>
+    <t>Open the Sizing tab. Leave the default values; scroll the panel if needed to capture every group.</t>
+  </si>
+  <si>
+    <t>/docs/bess/inputs/sizing</t>
+  </si>
+  <si>
+    <t>The Sizing tab's Contracted Capacity radio, Project/Contract Life, DFR Targets and Initial Sizing groups.</t>
+  </si>
+  <si>
+    <t>bess-inputs-sizing</t>
+  </si>
+  <si>
+    <t>bess/install/store-listing.png</t>
+  </si>
+  <si>
+    <t>Microsoft Store listing</t>
+  </si>
+  <si>
+    <t>The Microsoft Store app open on the BESS Desktop listing, with the Rensaar publisher name and the Get / Install button visible.</t>
+  </si>
+  <si>
+    <t>Open the Microsoft Store and search for BESS Desktop. Capture before installing so the button reads Get or Install.</t>
+  </si>
+  <si>
+    <t>/docs/bess/install/windows</t>
+  </si>
+  <si>
+    <t>The BESS Desktop listing in the Microsoft Store, showing the publisher and the Get button.</t>
+  </si>
+  <si>
+    <t>bess-install-store-listing</t>
+  </si>
+  <si>
+    <t>bess/intro/window.png</t>
+  </si>
+  <si>
+    <t>The main window</t>
+  </si>
+  <si>
+    <t>The whole main window: the navy top banner with its title, the left input notebook with the Simulate and Optimise buttons above its tabs, and the right result notebook with its four tabs showing a completed run.</t>
+  </si>
+  <si>
+    <t>Run Simulate to completion first, so the Dashboard tab has real charts in it rather than an empty panel. Maximise the window before capturing.</t>
+  </si>
+  <si>
+    <t>/docs/bess/intro</t>
+  </si>
+  <si>
+    <t>The BESS Desktop main window, with the input notebook on the left and the result notebook on the right.</t>
+  </si>
+  <si>
+    <t>bess-intro-window</t>
+  </si>
+  <si>
+    <t>bess/plant/designer-window.png</t>
+  </si>
+  <si>
+    <t>The Plant Layout &amp; SLD designer</t>
+  </si>
+  <si>
+    <t>The full designer window on the Plant Layout tab with default inputs: the three-group input form on the left (equipment counts, Equipment size, Spacing &amp; geo-reference), the Transformer Type control, and the empty drawing canvas with its toolbar, before Generate Layout is clicked.</t>
+  </si>
+  <si>
+    <t>Open Run ▸ BESS Plant Layout &amp; SLD… with the default inputs, on the Plant Layout tab.</t>
+  </si>
+  <si>
+    <t>Bracket the input form and label it 'shared inputs'; bracket the Plant Layout / Single Line Diagram tab strip.</t>
+  </si>
+  <si>
+    <t>/docs/bess/plant/overview</t>
+  </si>
+  <si>
+    <t>The plant designer window, showing the Plant Layout tab's input form on the left, alongside its drawing canvas.</t>
+  </si>
+  <si>
+    <t>bess-plant-overview-designer</t>
+  </si>
+  <si>
+    <t>bess/plant/generated-layout.png</t>
+  </si>
+  <si>
+    <t>A generated plant layout</t>
+  </si>
+  <si>
+    <t>The Plant Layout canvas after clicking Generate Layout with the default inputs, showing the south-to-north equipment stack, the routed connection lines, and the equipment count label.</t>
+  </si>
+  <si>
+    <t>Open the designer, leave the default inputs, and click ⚙  Generate Layout.</t>
+  </si>
+  <si>
+    <t>Callout the equipment count label.</t>
+  </si>
+  <si>
+    <t>/docs/bess/plant/generate-layout</t>
+  </si>
+  <si>
+    <t>The Plant Layout canvas after Generate Layout, showing the south-to-north stack of containers, PCS, LV panels, transformers and MV panels joined by connection lines.</t>
+  </si>
+  <si>
+    <t>bess-plant-generate-layout-result</t>
+  </si>
+  <si>
+    <t>bess/plant/generated-sld.png</t>
+  </si>
+  <si>
+    <t>A generated single-line diagram</t>
+  </si>
+  <si>
+    <t>The Single Line Diagram canvas after clicking ⚙  Generate SLD with the default inputs, showing battery, PCS and transformer symbols connected by wires, with LV and MV panels still drawn as rectangles.</t>
+  </si>
+  <si>
+    <t>With a layout already generated, switch to the Single Line Diagram tab and click ⚙  Generate SLD.</t>
+  </si>
+  <si>
+    <t>/docs/bess/plant/generate-sld</t>
+  </si>
+  <si>
+    <t>The Single Line Diagram canvas after Generate SLD, showing the same plant topology drawn as IEC schematic symbols.</t>
+  </si>
+  <si>
+    <t>bess-plant-generate-sld-result</t>
+  </si>
+  <si>
+    <t>bess/project-types/radio.png</t>
+  </si>
+  <si>
+    <t>The project type radio group</t>
+  </si>
+  <si>
+    <t>The project type radio group with all four options readable, plus the Peak-Shift dispatch checkbox beneath it.</t>
+  </si>
+  <si>
+    <t>Open the Data tab. Nothing changed from the default selection.</t>
+  </si>
+  <si>
+    <t>Outline the selected option.</t>
+  </si>
+  <si>
+    <t>/docs/bess/project-types</t>
+  </si>
+  <si>
+    <t>The four project type options on the Data tab, with Solar + Wind + BESS selected.</t>
+  </si>
+  <si>
+    <t>bess-project-types-radio</t>
+  </si>
+  <si>
+    <t>bess/results/dfr-table-columns.png</t>
+  </si>
+  <si>
+    <t>The DFR Table tab's column groups</t>
+  </si>
+  <si>
+    <t>The full DFR Table tab: the Month column, the delivery-percentage columns, the met/missed flag columns, the shortfall columns, the penalty columns and the export columns, with at least one green row and one red row visible.</t>
+  </si>
+  <si>
+    <t>Run Simulate to completion, then open the DFR Table tab. Prefer a run whose result includes at least one missed month, so both shading colours appear.</t>
+  </si>
+  <si>
+    <t>Bracket each column group and label it: delivery %, met/missed, shortfalls, penalty, export.</t>
+  </si>
+  <si>
+    <t>/docs/bess/results/dfr-table</t>
+  </si>
+  <si>
+    <t>The DFR Table tab listing one row per month, with its column groups and green/red row shading.</t>
+  </si>
+  <si>
+    <t>bess-results-dfr-table</t>
+  </si>
+  <si>
+    <t>bess/results/financials-table.png</t>
+  </si>
+  <si>
+    <t>The Financials tab</t>
+  </si>
+  <si>
+    <t>The headline summary lines at the top of the Financials tab, and the per-year table beneath it with at least one negative-NCF row and one replacement/augmentation row visible.</t>
+  </si>
+  <si>
+    <t>Run Simulate to completion, then open the Financials tab. Prefer a run whose result includes a replacement or augmentation year, so the yellow shading appears alongside any red text.</t>
+  </si>
+  <si>
+    <t>Callout the headline lines; bracket the per-year table.</t>
+  </si>
+  <si>
+    <t>/docs/bess/results/financials</t>
+  </si>
+  <si>
+    <t>The Financials tab's headline summary lines above the per-year cash-flow table.</t>
+  </si>
+  <si>
+    <t>bess-results-financials</t>
+  </si>
+  <si>
+    <t>bess/results/summary-report.png</t>
+  </si>
+  <si>
+    <t>The Summary tab</t>
+  </si>
+  <si>
+    <t>The dark console-style report text, and the full export toolbar: 📥 Export PDF, 💾 Save Plot, 📄 Save Report, 📊 Save DFR CSV, 🕒 Time-Series CSV, 📈 Sensitivity.</t>
+  </si>
+  <si>
+    <t>Run Simulate to completion, then open the Summary tab.</t>
+  </si>
+  <si>
+    <t>Number the six export buttons in order.</t>
+  </si>
+  <si>
+    <t>/docs/bess/results/summary</t>
+  </si>
+  <si>
+    <t>The Summary tab's plain-text project report above its row of export buttons.</t>
+  </si>
+  <si>
+    <t>bess-results-summary</t>
+  </si>
+  <si>
+    <t>2 — Valuable</t>
+  </si>
+  <si>
+    <t>bess/access/web-activation.png</t>
+  </si>
+  <si>
+    <t>The web activation page</t>
+  </si>
+  <si>
+    <t>The browser page that opens after clicking Get Free Access, addressed to this device's Device ID.</t>
+  </si>
+  <si>
+    <t>In the License window, click Get Free Access and capture the browser page it opens.</t>
+  </si>
+  <si>
+    <t>The browser page opened by Get Free Access, addressed to this device's Device ID.</t>
+  </si>
+  <si>
+    <t>bess-access-web-activation</t>
+  </si>
+  <si>
+    <t>bess/analysis/sensitivity/tornado.png</t>
+  </si>
+  <si>
+    <t>The Tornado Chart tab</t>
+  </si>
+  <si>
+    <t>The Tornado Chart tab: the Variation ± % and Metric inputs, the Run Tornado button, and the resulting horizontal bar chart sorted by swing magnitude.</t>
+  </si>
+  <si>
+    <t>Run Simulate or Optimise first to establish a base case, open Run ▸ Sensitivity Analysis…, switch to the Tornado Chart tab, and click ▶ Run Tornado.</t>
+  </si>
+  <si>
+    <t>/docs/bess/analysis/sensitivity</t>
+  </si>
+  <si>
+    <t>The Sensitivity Analysis window's Tornado Chart tab, showing a horizontal bar chart of each driver's swing sorted by size.</t>
+  </si>
+  <si>
+    <t>bess-analysis-sensitivity-tornado</t>
+  </si>
+  <si>
+    <t>bess/concepts/degradation-and-eol/soh-editor.png</t>
+  </si>
+  <si>
+    <t>The Year-by-Year SOH Profile editor</t>
+  </si>
+  <si>
+    <t>The Edit Year-by-Year SOH Profile dialog: the Year/SOH% table pre-filled from the Linear formula, and the Fill from Linear button.</t>
+  </si>
+  <si>
+    <t>Open the BESS tab, set Battery SOH Degradation to Custom Year-by-Year, then click Edit Year-by-Year SOH Profile….</t>
+  </si>
+  <si>
+    <t>/docs/bess/concepts/degradation-and-eol</t>
+  </si>
+  <si>
+    <t>The Year-by-Year SOH Profile editor, a table of project year against SOH percentage, with a Fill from Linear button above it.</t>
+  </si>
+  <si>
+    <t>bess-concepts-degradation-and-eol-soh-editor</t>
+  </si>
+  <si>
+    <t>bess/concepts/dfr/dfr-table.png</t>
+  </si>
+  <si>
+    <t>The DFR Table tab</t>
+  </si>
+  <si>
+    <t>The DFR Table tab: the full column set for a few months, with at least one green-shaded row (all targets met) and one red-shaded row (a target missed) visible together.</t>
+  </si>
+  <si>
+    <t>Callout the green and red row colours with a one-line key.</t>
+  </si>
+  <si>
+    <t>/docs/bess/concepts/dfr</t>
+  </si>
+  <si>
+    <t>The DFR Table tab listing one row per month, with green and red row shading marking months that met or missed their DFR targets.</t>
+  </si>
+  <si>
+    <t>bess-concepts-dfr-table</t>
+  </si>
+  <si>
+    <t>bess/concepts/how-dispatch-works/dispatch-chart.png</t>
+  </si>
+  <si>
+    <t>The dispatch chart</t>
+  </si>
+  <si>
+    <t>The Battery Charge / Discharge &amp; State of Charge panel from the Dashboard tab: the charge, discharge and grid-charge fills on the left axis, the state-of-charge line on the twin right axis, and the purple shading on any day with grid charging.</t>
+  </si>
+  <si>
+    <t>Run Simulate to completion, then open the Dashboard tab and crop to the second panel.</t>
+  </si>
+  <si>
+    <t>Bracket the panel; label the left axis MWh and the right axis SOC.</t>
+  </si>
+  <si>
+    <t>/docs/bess/concepts/how-dispatch-works</t>
+  </si>
+  <si>
+    <t>The Dashboard's Battery Charge / Discharge &amp; State of Charge panel, showing charge, discharge and grid-charge fills against a state-of-charge line.</t>
+  </si>
+  <si>
+    <t>bess-concepts-how-dispatch-works-chart</t>
+  </si>
+  <si>
+    <t>bess/first-analysis/simulate.png</t>
+  </si>
+  <si>
+    <t>Running Simulate</t>
+  </si>
+  <si>
+    <t>The Simulate button and, below it, the status bar reporting Financial model: year &lt;n&gt;/&lt;total&gt;… with the progress bar advancing.</t>
+  </si>
+  <si>
+    <t>With a generation profile loaded (or Standalone BESS chosen) and the default peak window left as-is, click Simulate and capture while the status bar is still updating.</t>
+  </si>
+  <si>
+    <t>The status bar reporting the financial model's year-by-year progress while Simulate runs.</t>
+  </si>
+  <si>
+    <t>bess-first-analysis-simulate</t>
+  </si>
+  <si>
+    <t>bess/getting-started/tabs.png</t>
+  </si>
+  <si>
+    <t>The input and result tab strips</t>
+  </si>
+  <si>
+    <t>A close view of both tab strips: Data, Peak, Sizing, BESS, Degrad., CAPEX, OPEX, Finance on the left; Dashboard, DFR Table, Financials, Summary on the right.</t>
+  </si>
+  <si>
+    <t>Straight after launch, with both notebooks showing their default first tab.</t>
+  </si>
+  <si>
+    <t>Number the input tabs 1 to 8 in order.</t>
+  </si>
+  <si>
+    <t>The eight input tabs on the left and the four result tabs on the right, side by side.</t>
+  </si>
+  <si>
+    <t>bess-getting-started-tabs</t>
+  </si>
+  <si>
+    <t>bess/inputs/capex.png</t>
+  </si>
+  <si>
+    <t>The CAPEX tab</t>
+  </si>
+  <si>
+    <t>The whole CAPEX tab: the Solar CAPEX, Wind CAPEX and BESS CAPEX fields, and the in-panel Crore note.</t>
+  </si>
+  <si>
+    <t>Open the CAPEX tab. Leave the default values — the BESS CAPEX field itself reads 1.5.</t>
+  </si>
+  <si>
+    <t>/docs/bess/inputs/capex</t>
+  </si>
+  <si>
+    <t>The CAPEX tab's Solar, Wind and BESS capital cost fields.</t>
+  </si>
+  <si>
+    <t>bess-inputs-capex</t>
+  </si>
+  <si>
+    <t>bess/inputs/degradation.png</t>
+  </si>
+  <si>
+    <t>The Degrad. tab</t>
+  </si>
+  <si>
+    <t>The whole Degrad. tab: the two generation-loss fields and the in-panel formula caption.</t>
+  </si>
+  <si>
+    <t>Open the Degrad. tab. Leave the default values.</t>
+  </si>
+  <si>
+    <t>/docs/bess/inputs/degradation</t>
+  </si>
+  <si>
+    <t>The Degrad. tab's Generation Loss Year-1 and Year-2+ fields.</t>
+  </si>
+  <si>
+    <t>bess-inputs-degradation</t>
+  </si>
+  <si>
+    <t>bess/install/store-updates.png</t>
+  </si>
+  <si>
+    <t>Store Library and updates</t>
+  </si>
+  <si>
+    <t>The Store's Library page, with BESS Desktop listed and the Get updates button visible.</t>
+  </si>
+  <si>
+    <t>Open the Microsoft Store, then the Library from the left-hand navigation.</t>
+  </si>
+  <si>
+    <t>/docs/bess/install/updates</t>
+  </si>
+  <si>
+    <t>The Microsoft Store Library page listing installed applications and any updates waiting for them.</t>
+  </si>
+  <si>
+    <t>bess-install-store-updates</t>
+  </si>
+  <si>
+    <t>bess/plant/cad-toolbar.png</t>
+  </si>
+  <si>
+    <t>The CAD toolbar</t>
+  </si>
+  <si>
+    <t>Both toolbar rows in full: the drawing tools (Select, Move, Pan, Line, Rect, Circle, Polygon, Text, Measure, Dimension, Rotate, Edit Text) and the second row (Copy, Paste, Delete, Undo, Redo, Fit, Snap, Ortho, Import), plus the sheet-size combobox, Add Sheet, and the six layer toggles.</t>
+  </si>
+  <si>
+    <t>Open either canvas of the designer and crop to the toolbar strip, including the sheet and layer controls.</t>
+  </si>
+  <si>
+    <t>Bracket row 1 as drawing tools and row 2 as edit/canvas controls; circle the layer toggles.</t>
+  </si>
+  <si>
+    <t>/docs/bess/plant/cad-editor</t>
+  </si>
+  <si>
+    <t>The drawing editor's two toolbar rows, plus the sheet-size combobox and the layer toggles.</t>
+  </si>
+  <si>
+    <t>bess-plant-cad-editor-toolbar</t>
+  </si>
+  <si>
+    <t>bess/results/dashboard-toolbar.png</t>
+  </si>
+  <si>
+    <t>The Dashboard toolbar and day slider</t>
+  </si>
+  <si>
+    <t>The narrow toolbar strip above the six panels, ending in the ⛶ Maximize button, plus the Day slider and its scroll instruction beneath the first two panels.</t>
+  </si>
+  <si>
+    <t>Run Simulate to completion, then open the Dashboard tab and crop to the toolbar row and the slider beneath the first two panels.</t>
+  </si>
+  <si>
+    <t>Circle the ⛶ Maximize button.</t>
+  </si>
+  <si>
+    <t>/docs/bess/results/dashboard</t>
+  </si>
+  <si>
+    <t>The toolbar above the Dashboard's six panels, ending in the Maximize button, with the day slider beneath the first two panels.</t>
+  </si>
+  <si>
+    <t>bess-results-dashboard</t>
   </si>
   <si>
     <t>Topic</t>
@@ -141,7 +861,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -152,6 +872,14 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFB4530A"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
     </font>
   </fonts>
   <fills count="3">
@@ -179,15 +907,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -578,8 +1312,1128 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K33"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -594,124 +2448,124 @@
     <col min="2" max="2" width="108" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>40</v>
+    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
